--- a/414-rc---contact/ig/ValueSet-tddui-contact-related-person-relashionship.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-contact-related-person-relashionship.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:08:59+00:00</t>
+    <t>2026-02-04T16:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
